--- a/experiments_results.xlsx
+++ b/experiments_results.xlsx
@@ -441,20 +441,20 @@
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="35" customWidth="1" min="17" max="17"/>
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -564,54 +564,48 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6846561396414218</v>
+        <v>1.2225</v>
       </c>
       <c r="E2" t="n">
-        <v>0.910924333426347</v>
+        <v>1.7523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8297831412282347</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24.82112175492617</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9520671648595923</v>
+        <v>3.0705</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7666972624082454</v>
+        <v>1.028014402392509</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3558628730232657</v>
+        <v>0.4650044066881193</v>
       </c>
       <c r="K2" t="n">
-        <v>2.00927831608037</v>
+        <v>1.625519971304106</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7150275542637099</v>
+        <v>0.7558739544659985</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02580741126388054</v>
+        <v>-5.432842080328228e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03347331401972743</v>
+        <v>-0.0003020795846336141</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1724203975925858</v>
+        <v>-0.001695996944446386</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02286601066589355</v>
+        <v>0.0004119873046875</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>max_depth=20, min_samples_leaf=2, min_samples_split=2, n_estimators=100</t>
+          <t>C=100, gamma=0.1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -625,59 +619,53 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8055769824845641</v>
+        <v>0.5589</v>
       </c>
       <c r="E3" t="n">
-        <v>1.208373727586369</v>
+        <v>0.8966</v>
       </c>
       <c r="F3" t="n">
-        <v>1.460167065520976</v>
-      </c>
-      <c r="G3" t="n">
-        <v>107.4811497554672</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.6449622118838467</v>
+        <v>0.8038</v>
       </c>
       <c r="I3" t="n">
-        <v>1.206294976994013</v>
+        <v>1.010026713223968</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5180903053668426</v>
+        <v>0.3920744377771075</v>
       </c>
       <c r="K3" t="n">
-        <v>1.829849454108731</v>
+        <v>0.7188679460737601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9480272624545427</v>
+        <v>0.2818497497135979</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02960343901580158</v>
+        <v>0.0001915250752908542</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4866764680766803</v>
+        <v>-0.00021594138764734</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5964048253068203</v>
+        <v>0.001731647091980847</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02268004417419434</v>
+        <v>0.0002484321594238281</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>max_depth=None, min_samples_leaf=1, min_samples_split=2, n_estimators=100</t>
+          <t>C=1000, gamma=0.01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dataset1</t>
+          <t>dataset1_poly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -686,59 +674,53 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.421826011974136</v>
+        <v>1.4371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5892536463421583</v>
+        <v>2.0783</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3472198597275294</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13.81032916006913</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9799426724081668</v>
+        <v>4.3193</v>
       </c>
       <c r="I4" t="n">
-        <v>71.00909020855119</v>
+        <v>1.027251937515628</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3588082282604724</v>
+        <v>0.2658887902814437</v>
       </c>
       <c r="K4" t="n">
-        <v>1.675458621039349</v>
+        <v>3.658645727185482</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6011683393388629</v>
+        <v>0.9727928891286088</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02563756470806998</v>
+        <v>-1.700264923007064e-05</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1723452431394286</v>
+        <v>-0.001226243080473738</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2527920233688631</v>
+        <v>0.0007057806557178822</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03399395942687988</v>
+        <v>0.0002675056457519531</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>max_depth=10, min_samples_leaf=1, min_samples_split=2, n_estimators=100</t>
+          <t>C=500, gamma=0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dataset1</t>
+          <t>dataset1_poly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -747,54 +729,48 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.000135114992143</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.700717682093082</v>
+        <v>1.1379</v>
       </c>
       <c r="F5" t="n">
-        <v>2.892440634184064</v>
-      </c>
-      <c r="G5" t="n">
-        <v>130.92553352968</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2967066924964544</v>
+        <v>1.2949</v>
       </c>
       <c r="I5" t="n">
-        <v>100013481.4671027</v>
+        <v>1.012123886177744</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5460511911873694</v>
+        <v>0.3974546812249474</v>
       </c>
       <c r="K5" t="n">
-        <v>1.493190176186075</v>
+        <v>1.015282703381083</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8153582743756842</v>
+        <v>0.4035288672000779</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.002312719227554541</v>
+        <v>-0.0001560324303772661</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2480435481915744</v>
+        <v>-0.002179645250025555</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5295912800566724</v>
+        <v>0.002425668389359226</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02282524108886719</v>
+        <v>0.0002644062042236328</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>max_depth=None, min_samples_leaf=1, min_samples_split=2, n_estimators=100</t>
+          <t>C=500, gamma=0.001</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>LinearTreeRegressor</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -808,54 +784,48 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5301643410226698</v>
+        <v>0.846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8372317200877164</v>
+        <v>1.1594</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7009569531210363</v>
-      </c>
-      <c r="G6" t="n">
-        <v>25.98589773364344</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.9595088735778116</v>
+        <v>1.3441</v>
       </c>
       <c r="I6" t="n">
-        <v>1.249674908278676</v>
+        <v>1.231434150261149</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3782718333592945</v>
+        <v>0.4388295417560584</v>
       </c>
       <c r="K6" t="n">
-        <v>1.489623899286127</v>
+        <v>1.482015901882171</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5634827633987843</v>
+        <v>0.6503523634864399</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06848025428658713</v>
+        <v>0.01230275465359999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.004473631842198526</v>
+        <v>-0.1529865595353218</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4789606629961318</v>
+        <v>0.4107278248604461</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003690719604492188</v>
+        <v>0.002233505249023438</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>learning_rate=0.15, max_depth=None, min_samples_leaf=4, min_samples_split=2, n_estimators=50, subsample=0.8</t>
+          <t>base_estimator__alpha=0.1, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=0.1), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=5, min_samples_split=10, n_jobs=None, split_features=None</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>LinearTreeRegressor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,158 +839,158 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5264234657130868</v>
+        <v>0.6773</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7307407402611995</v>
+        <v>1.4108</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5339820294774859</v>
-      </c>
-      <c r="G7" t="n">
-        <v>96.27556826982743</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.87016294017574</v>
+        <v>1.9903</v>
       </c>
       <c r="I7" t="n">
-        <v>416.848905050461</v>
+        <v>2.200867132526699</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5605059041629158</v>
+        <v>0.4886531230783967</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75262975752466</v>
+        <v>0.5657549392263534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9823593269041915</v>
+        <v>0.2764579228365174</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9393889015130247</v>
+        <v>-0.0002901256913849227</v>
       </c>
       <c r="N7" t="n">
-        <v>1.110017650041022</v>
+        <v>-0.04517945855973821</v>
       </c>
       <c r="O7" t="n">
-        <v>3.087160781697726</v>
+        <v>0.2601289621426481</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003628730773925781</v>
+        <v>0.01761484146118164</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>learning_rate=0.15, max_depth=10, min_samples_leaf=1, min_samples_split=10, n_estimators=100, subsample=1.0</t>
+          <t>base_estimator__alpha=0.1, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=0.1), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=5, min_samples_split=10, n_jobs=None, split_features=None</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LinearTreeRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dataset1</t>
+          <t>dataset1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFR_err</t>
+          <t>MFR</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8719209999999999</v>
+        <v>2.6325</v>
       </c>
       <c r="E8" t="n">
-        <v>1.443629</v>
+        <v>3.5692</v>
       </c>
       <c r="F8" t="n">
-        <v>2.084066</v>
-      </c>
-      <c r="G8" t="n">
-        <v>198.9501</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.879613</v>
+        <v>12.739</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1162</v>
+        <v>1.470505238563703</v>
       </c>
       <c r="J8" t="n">
-        <v>6.910117</v>
+        <v>0.2644758288618836</v>
       </c>
       <c r="K8" t="n">
-        <v>0.123489</v>
+        <v>2.828108087746713</v>
       </c>
       <c r="L8" t="n">
-        <v>0.853325</v>
+        <v>0.7479662332625668</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.006782892435927277</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.06927381629180306</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.116545544371374</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0007069110870361328</v>
+        <v>0.007422685623168945</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bootstrap=True, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LinearTreeRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dataset1</t>
+          <t>dataset1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DD_err</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.613324</v>
+        <v>1.4679</v>
       </c>
       <c r="E9" t="n">
-        <v>0.859745</v>
+        <v>2.4107</v>
       </c>
       <c r="F9" t="n">
-        <v>0.739161</v>
-      </c>
-      <c r="G9" t="n">
-        <v>57.6811</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8202739999999999</v>
+        <v>5.8117</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1451</v>
+        <v>1.907942195999853</v>
       </c>
       <c r="J9" t="n">
-        <v>1.294263</v>
+        <v>0.3391909259900333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.327674</v>
+        <v>1.296114040687701</v>
       </c>
       <c r="L9" t="n">
-        <v>0.424096</v>
+        <v>0.4396301250414543</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.01435855625450319</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.01127660457505229</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.1092292247477952</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0006628036499023438</v>
+        <v>0.01815247535705566</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>bootstrap=True, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>ExtraTreesRegressor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1034,54 +1004,48 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.010506058825768</v>
+        <v>3.1445</v>
       </c>
       <c r="E10" t="n">
-        <v>1.306730209451553</v>
+        <v>4.5727</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7075438402933</v>
-      </c>
-      <c r="G10" t="n">
-        <v>54.69256606678011</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9013628822698809</v>
+        <v>20.9098</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2486221970646812</v>
+        <v>1.171313707201319</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2583034773163324</v>
+        <v>0.2372482325195863</v>
       </c>
       <c r="K10" t="n">
-        <v>3.518005869634139</v>
+        <v>3.130281705639715</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9087131493457659</v>
+        <v>0.7426538043239006</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03125487356015683</v>
+        <v>-0.002044925826907989</v>
       </c>
       <c r="N10" t="n">
-        <v>0.05026617898968011</v>
+        <v>0.01548235376622814</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1575582731801804</v>
+        <v>-0.05379224246752059</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0001678466796875</v>
+        <v>0.007703065872192383</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>C=17.800503617543782, gamma=0.676376028878698</t>
+          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>ExtraTreesRegressor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1095,59 +1059,53 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.789829279159925</v>
+        <v>1.8584</v>
       </c>
       <c r="E11" t="n">
-        <v>3.348834788970778</v>
+        <v>2.8979</v>
       </c>
       <c r="F11" t="n">
-        <v>11.21469444382095</v>
-      </c>
-      <c r="G11" t="n">
-        <v>306.6840069785694</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-1.726838869161925</v>
+        <v>8.397600000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7308465803063111</v>
+        <v>1.468031628588453</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2788715224682745</v>
+        <v>0.2073793635488007</v>
       </c>
       <c r="K11" t="n">
-        <v>2.330574232220089</v>
+        <v>1.513946310615912</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6499307843645461</v>
+        <v>0.3139612244163763</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.004120187815993866</v>
+        <v>0.006466355442039965</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08205126384535938</v>
+        <v>0.008470695230302507</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1148985252334251</v>
+        <v>0.1022156985444459</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001599788665771484</v>
+        <v>0.04069161415100098</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>C=4.294720079072475, gamma=0.13661664071224597</t>
+          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>GradientBoostingRegressor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dataset1poly</t>
+          <t>dataset1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1156,59 +1114,53 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9174303097302798</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.095697130009032</v>
+        <v>1.042</v>
       </c>
       <c r="F12" t="n">
-        <v>1.20055220071003</v>
-      </c>
-      <c r="G12" t="n">
-        <v>72.26831920783576</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9306495060517754</v>
+        <v>1.0858</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2239673696177072</v>
+        <v>1.881512537819904</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1955931486755916</v>
+        <v>0.3235280151557353</v>
       </c>
       <c r="K12" t="n">
-        <v>3.757655164000783</v>
+        <v>2.019712600800497</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7349716051640098</v>
+        <v>0.6534336121572928</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00946188758202323</v>
+        <v>0.09687738645483793</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0245153717038306</v>
+        <v>0.37631278195179</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2302201884467657</v>
+        <v>1.455055303594941</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0002691745758056641</v>
+        <v>0.0004868507385253906</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>C=179.41783365178588, gamma=0.16318896221372614</t>
+          <t>alpha=0.9, ccp_alpha=0.0, criterion=friedman_mse, init=None, learning_rate=0.05, loss=squared_error, max_depth=3, max_features=None, max_leaf_nodes=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, n_estimators=100, n_iter_no_change=None, random_state=42, subsample=1.0, tol=0.0001, validation_fraction=0.1, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>GradientBoostingRegressor</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dataset1poly</t>
+          <t>dataset1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1217,47 +1169,41 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.201179238925369</v>
+        <v>1.0247</v>
       </c>
       <c r="E13" t="n">
-        <v>1.543700120806033</v>
+        <v>1.7155</v>
       </c>
       <c r="F13" t="n">
-        <v>2.383010062976562</v>
-      </c>
-      <c r="G13" t="n">
-        <v>188.7582199725084</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4205740960772415</v>
+        <v>2.9428</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5893573599003294</v>
+        <v>4.884474072090205</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3572368094679534</v>
+        <v>0.3369397604527993</v>
       </c>
       <c r="K13" t="n">
-        <v>2.867173106181723</v>
+        <v>0.9507065053202961</v>
       </c>
       <c r="L13" t="n">
-        <v>1.02425977264468</v>
+        <v>0.3203308255329362</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01680377114536841</v>
+        <v>0.05533928672201867</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06654464671237889</v>
+        <v>0.1825669948025412</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1368772922225924</v>
+        <v>0.09334555476072186</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001561641693115234</v>
+        <v>0.0008516311645507812</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>C=256.0, gamma=0.06710500123550742</t>
+          <t>alpha=0.9, ccp_alpha=0.0, criterion=friedman_mse, init=None, learning_rate=0.05, loss=squared_error, max_depth=3, max_features=None, max_leaf_nodes=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, n_estimators=100, n_iter_no_change=None, random_state=42, subsample=1.0, tol=0.0001, validation_fraction=0.1, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>

--- a/experiments_results.xlsx
+++ b/experiments_results.xlsx
@@ -455,7 +455,7 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="35" customWidth="1" min="17" max="17"/>
   </cols>
@@ -585,16 +585,16 @@
         <v>0.7558739544659985</v>
       </c>
       <c r="M2" t="n">
-        <v>-5.432842080328228e-05</v>
+        <v>0.0003505284218586694</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0003020795846336141</v>
+        <v>6.241512253452908e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.001695996944446386</v>
+        <v>-0.0006977097331907824</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004119873046875</v>
+        <v>0.0005750656127929688</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>0.2818497497135979</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001915250752908542</v>
+        <v>-0.0001350483203320043</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00021594138764734</v>
+        <v>-0.000642220869373227</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001731647091980847</v>
+        <v>0.002621406334016983</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002484321594238281</v>
+        <v>0.0004737377166748047</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -695,16 +695,16 @@
         <v>0.9727928891286088</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.700264923007064e-05</v>
+        <v>0.0001393678440990816</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.001226243080473738</v>
+        <v>-0.0004296432854840813</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007057806557178822</v>
+        <v>0.0007264231861186331</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0002675056457519531</v>
+        <v>0.0006351470947265625</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -750,16 +750,16 @@
         <v>0.4035288672000779</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0001560324303772661</v>
+        <v>0.0001358697636903187</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.002179645250025555</v>
+        <v>-0.001598847015540611</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002425668389359226</v>
+        <v>-0.003356736311770497</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002644062042236328</v>
+        <v>0.0004901885986328125</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         <v>0.6503523634864399</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01230275465359999</v>
+        <v>0.01455441875410851</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1529865595353218</v>
+        <v>-0.1165514810501328</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4107278248604461</v>
+        <v>0.3294733590254848</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002233505249023438</v>
+        <v>0.001428842544555664</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         <v>0.2764579228365174</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0002901256913849227</v>
+        <v>-0.005147337478558787</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04517945855973821</v>
+        <v>0.1070473776145579</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2601289621426481</v>
+        <v>0.1451990603714351</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01761484146118164</v>
+        <v>0.002348423004150391</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         <v>0.7479662332625668</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006782892435927277</v>
+        <v>0.01583248224605282</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06927381629180306</v>
+        <v>0.01175789246990299</v>
       </c>
       <c r="O8" t="n">
-        <v>0.116545544371374</v>
+        <v>0.01851572635535855</v>
       </c>
       <c r="P8" t="n">
-        <v>0.007422685623168945</v>
+        <v>0.008124351501464844</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -970,16 +970,16 @@
         <v>0.4396301250414543</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01435855625450319</v>
+        <v>-0.00381615439901504</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01127660457505229</v>
+        <v>-0.05443081588666517</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1092292247477952</v>
+        <v>0.02615407383879495</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01815247535705566</v>
+        <v>0.02886557579040527</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         <v>0.7426538043239006</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.002044925826907989</v>
+        <v>0.008988447373934316</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01548235376622814</v>
+        <v>0.007968594265890043</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.05379224246752059</v>
+        <v>0.0611933697197927</v>
       </c>
       <c r="P10" t="n">
-        <v>0.007703065872192383</v>
+        <v>0.008952617645263672</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         <v>0.3139612244163763</v>
       </c>
       <c r="M11" t="n">
-        <v>0.006466355442039965</v>
+        <v>0.004189030733484831</v>
       </c>
       <c r="N11" t="n">
-        <v>0.008470695230302507</v>
+        <v>-0.01101508025198876</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1022156985444459</v>
+        <v>0.007930930027972833</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04069161415100098</v>
+        <v>0.04862546920776367</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0.6534336121572928</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09687738645483793</v>
+        <v>0.0426754187976977</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37631278195179</v>
+        <v>0.4447519460525681</v>
       </c>
       <c r="O12" t="n">
-        <v>1.455055303594941</v>
+        <v>0.7523464877596847</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004868507385253906</v>
+        <v>0.0004611015319824219</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         <v>0.3203308255329362</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05533928672201867</v>
+        <v>0.04173844462649846</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1825669948025412</v>
+        <v>0.03150180304862088</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09334555476072186</v>
+        <v>0.1877523913451777</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0008516311645507812</v>
+        <v>0.0006844997406005859</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>

--- a/experiments_results.xlsx
+++ b/experiments_results.xlsx
@@ -449,13 +449,13 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
     <col width="35" customWidth="1" min="17" max="17"/>
   </cols>
@@ -564,41 +564,41 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.2225</v>
+        <v>0.7662</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7523</v>
+        <v>1.0052</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0705</v>
+        <v>1.0105</v>
       </c>
       <c r="I2" t="n">
-        <v>1.028014402392509</v>
+        <v>0.9823812636159142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4650044066881193</v>
+        <v>0.7444924244983386</v>
       </c>
       <c r="K2" t="n">
-        <v>1.625519971304106</v>
+        <v>0.3225318974695015</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7558739544659985</v>
+        <v>0.240122561770043</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003505284218586694</v>
+        <v>-0.01487682818040873</v>
       </c>
       <c r="N2" t="n">
-        <v>6.241512253452908e-05</v>
+        <v>0.1243407678034236</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0006977097331907824</v>
+        <v>0.5016534039056355</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005750656127929688</v>
+        <v>0.0005509853363037109</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>C=100, gamma=0.1</t>
+          <t>C=29.857055729177844, gamma=0.15389305166811462</t>
         </is>
       </c>
     </row>
@@ -619,48 +619,48 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5589</v>
+        <v>1.4465</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8966</v>
+        <v>2.4481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8038</v>
+        <v>5.9932</v>
       </c>
       <c r="I3" t="n">
-        <v>1.010026713223968</v>
+        <v>1.303048876369187</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3920744377771075</v>
+        <v>0.4084178707443971</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7188679460737601</v>
+        <v>0.529132035947295</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2818497497135979</v>
+        <v>0.2161069835484207</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0001350483203320043</v>
+        <v>0.01382198166037124</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000642220869373227</v>
+        <v>0.0001361150265613864</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002621406334016983</v>
+        <v>0.05745972893141829</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004737377166748047</v>
+        <v>0.0003435611724853516</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>C=1000, gamma=0.01</t>
+          <t>C=1, gamma=scale</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>SVR_poly</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -674,48 +674,48 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.4371</v>
+        <v>0.9048</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0783</v>
+        <v>1.3349</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3193</v>
+        <v>1.7818</v>
       </c>
       <c r="I4" t="n">
-        <v>1.027251937515628</v>
+        <v>1.10079198459697</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2658887902814437</v>
+        <v>0.8087230324348924</v>
       </c>
       <c r="K4" t="n">
-        <v>3.658645727185482</v>
+        <v>0.287373384659924</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9727928891286088</v>
+        <v>0.2324054831704828</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001393678440990816</v>
+        <v>-0.00895315061721659</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0004296432854840813</v>
+        <v>0.05253091296138067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007264231861186331</v>
+        <v>0.1137540746108816</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0006351470947265625</v>
+        <v>0.0003705024719238281</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>C=500, gamma=0.001</t>
+          <t>C=61.765013162827636, gamma=0.013554087448936302</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>SVR_poly</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -729,41 +729,41 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6556999999999999</v>
+        <v>1.568</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1379</v>
+        <v>2.5875</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2949</v>
+        <v>6.6953</v>
       </c>
       <c r="I5" t="n">
-        <v>1.012123886177744</v>
+        <v>1.567666679765567</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3974546812249474</v>
+        <v>0.4827573058496599</v>
       </c>
       <c r="K5" t="n">
-        <v>1.015282703381083</v>
+        <v>0.5222833181963367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4035288672000779</v>
+        <v>0.2521360924102572</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0001358697636903187</v>
+        <v>0.002378964036763844</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.001598847015540611</v>
+        <v>0.01997059654956247</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.003356736311770497</v>
+        <v>-0.03252571602281806</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0004901885986328125</v>
+        <v>0.003354310989379883</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>C=500, gamma=0.001</t>
+          <t>C=3, gamma=scale</t>
         </is>
       </c>
     </row>
@@ -784,41 +784,41 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.846</v>
+        <v>1.0579</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1594</v>
+        <v>1.2683</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3441</v>
+        <v>1.6086</v>
       </c>
       <c r="I6" t="n">
-        <v>1.231434150261149</v>
+        <v>1.198437887333093</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4388295417560584</v>
+        <v>0.3979478525209206</v>
       </c>
       <c r="K6" t="n">
-        <v>1.482015901882171</v>
+        <v>1.18666463141507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6503523634864399</v>
+        <v>0.4722306457136356</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01455441875410851</v>
+        <v>0.02202588933269249</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1165514810501328</v>
+        <v>-0.06351759186169516</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3294733590254848</v>
+        <v>0.03034236634852726</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001428842544555664</v>
+        <v>0.0005502700805664062</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>base_estimator__alpha=0.1, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=0.1), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=5, min_samples_split=10, n_jobs=None, split_features=None</t>
+          <t>base_estimator__alpha=5.0, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=5.0), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=10, min_samples_split=20, n_jobs=None, split_features=None</t>
         </is>
       </c>
     </row>
@@ -839,41 +839,41 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6773</v>
+        <v>2.104</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4108</v>
+        <v>3.2591</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9903</v>
+        <v>10.6218</v>
       </c>
       <c r="I7" t="n">
-        <v>2.200867132526699</v>
+        <v>1.660923039070698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4886531230783967</v>
+        <v>0.2648722110764834</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5657549392263534</v>
+        <v>1.785657664097966</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2764579228365174</v>
+        <v>0.4729710963640188</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.005147337478558787</v>
+        <v>0.01339415011084228</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1070473776145579</v>
+        <v>0.00512983418523805</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1451990603714351</v>
+        <v>-0.03527947037138877</v>
       </c>
       <c r="P7" t="n">
-        <v>0.002348423004150391</v>
+        <v>0.0005972385406494141</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>base_estimator__alpha=0.1, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=0.1), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=5, min_samples_split=10, n_jobs=None, split_features=None</t>
+          <t>base_estimator__alpha=5.0, base_estimator__copy_X=True, base_estimator__fit_intercept=True, base_estimator__max_iter=None, base_estimator__positive=False, base_estimator__random_state=None, base_estimator__solver=auto, base_estimator__tol=0.0001, base_estimator=Ridge(alpha=5.0), categorical_features=None, criterion=mse, linear_features=None, max_bins=25, max_depth=3, min_impurity_decrease=0.0, min_samples_leaf=10, min_samples_split=20, n_jobs=None, split_features=None</t>
         </is>
       </c>
     </row>
@@ -894,37 +894,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.6325</v>
+        <v>1.8565</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5692</v>
+        <v>2.7853</v>
       </c>
       <c r="F8" t="n">
-        <v>12.739</v>
+        <v>7.7578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.470505238563703</v>
+        <v>1.626933281015934</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2644758288618836</v>
+        <v>0.5794164465660977</v>
       </c>
       <c r="K8" t="n">
-        <v>2.828108087746713</v>
+        <v>1.958269340745401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7479662332625668</v>
+        <v>1.134653468628199</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01583248224605282</v>
+        <v>-0.002218995264653381</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01175789246990299</v>
+        <v>0.00365734907877582</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01851572635535855</v>
+        <v>0.05320476099839876</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008124351501464844</v>
+        <v>0.008507490158081055</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -949,41 +949,41 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.4679</v>
+        <v>1.9044</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4107</v>
+        <v>2.4821</v>
       </c>
       <c r="F9" t="n">
-        <v>5.8117</v>
+        <v>6.1608</v>
       </c>
       <c r="I9" t="n">
-        <v>1.907942195999853</v>
+        <v>1.653762953985138</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3391909259900333</v>
+        <v>0.603784372727985</v>
       </c>
       <c r="K9" t="n">
-        <v>1.296114040687701</v>
+        <v>2.077461396096401</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4396301250414543</v>
+        <v>1.254338731946513</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.00381615439901504</v>
+        <v>0.02898870311051417</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05443081588666517</v>
+        <v>0.06790207403199719</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02615407383879495</v>
+        <v>0.09405967471274275</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02886557579040527</v>
+        <v>0.007846832275390625</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>bootstrap=True, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
+          <t>bootstrap=True, ccp_alpha=0.0, criterion=squared_error, max_depth=None, max_features=None, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
@@ -1004,41 +1004,41 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.1445</v>
+        <v>1.5577</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5727</v>
+        <v>2.1796</v>
       </c>
       <c r="F10" t="n">
-        <v>20.9098</v>
+        <v>4.7507</v>
       </c>
       <c r="I10" t="n">
-        <v>1.171313707201319</v>
+        <v>1.439903396194011</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2372482325195863</v>
+        <v>0.5359503407444023</v>
       </c>
       <c r="K10" t="n">
-        <v>3.130281705639715</v>
+        <v>2.062410111905875</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7426538043239006</v>
+        <v>1.105349407590158</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008988447373934316</v>
+        <v>-0.003203738030492594</v>
       </c>
       <c r="N10" t="n">
-        <v>0.007968594265890043</v>
+        <v>0.01374401267961648</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0611933697197927</v>
+        <v>0.1010977649417705</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008952617645263672</v>
+        <v>0.008417844772338867</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
+          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=None, max_features=sqrt, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=1, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
@@ -1059,41 +1059,41 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.8584</v>
+        <v>1.4484</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8979</v>
+        <v>1.8644</v>
       </c>
       <c r="F11" t="n">
-        <v>8.397600000000001</v>
+        <v>3.4759</v>
       </c>
       <c r="I11" t="n">
-        <v>1.468031628588453</v>
+        <v>2.089146196996778</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2073793635488007</v>
+        <v>0.649693987355873</v>
       </c>
       <c r="K11" t="n">
-        <v>1.513946310615912</v>
+        <v>1.655773629438342</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3139612244163763</v>
+        <v>1.075746177965442</v>
       </c>
       <c r="M11" t="n">
-        <v>0.004189030733484831</v>
+        <v>0.008425145719275065</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01101508025198876</v>
+        <v>0.1158581273176713</v>
       </c>
       <c r="O11" t="n">
-        <v>0.007930930027972833</v>
+        <v>0.1718444165250167</v>
       </c>
       <c r="P11" t="n">
-        <v>0.04862546920776367</v>
+        <v>0.00820159912109375</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=3, max_features=1.0, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=2, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
+          <t>bootstrap=False, ccp_alpha=0.0, criterion=squared_error, max_depth=None, max_features=None, max_leaf_nodes=None, max_samples=None, min_impurity_decrease=0.0, min_samples_leaf=1, min_samples_split=5, min_weight_fraction_leaf=0.0, monotonic_cst=None, n_estimators=100, n_jobs=None, oob_score=False, random_state=42, verbose=0, warm_start=False</t>
         </is>
       </c>
     </row>
@@ -1114,37 +1114,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7364000000000001</v>
+        <v>1.183</v>
       </c>
       <c r="E12" t="n">
-        <v>1.042</v>
+        <v>1.7147</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0858</v>
+        <v>2.9401</v>
       </c>
       <c r="I12" t="n">
-        <v>1.881512537819904</v>
+        <v>3.110704696958999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3235280151557353</v>
+        <v>0.577769371015079</v>
       </c>
       <c r="K12" t="n">
-        <v>2.019712600800497</v>
+        <v>1.581781281894054</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6534336121572928</v>
+        <v>0.9139047821010463</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0426754187976977</v>
+        <v>0.01732693543341739</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4447519460525681</v>
+        <v>0.1911283651513789</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7523464877596847</v>
+        <v>0.185369845332556</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004611015319824219</v>
+        <v>0.0004484653472900391</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1169,37 +1169,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.0247</v>
+        <v>1.3974</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7155</v>
+        <v>2.0781</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9428</v>
+        <v>4.3186</v>
       </c>
       <c r="I13" t="n">
-        <v>4.884474072090205</v>
+        <v>5.193725068795724</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3369397604527993</v>
+        <v>0.4876557419597148</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9507065053202961</v>
+        <v>2.010461277599617</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3203308255329362</v>
+        <v>0.9804129908856749</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04173844462649846</v>
+        <v>-0.05347356404569381</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03150180304862088</v>
+        <v>0.1799033752037129</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1877523913451777</v>
+        <v>0.174618457086223</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0006844997406005859</v>
+        <v>0.0004687309265136719</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>

--- a/experiments_results.xlsx
+++ b/experiments_results.xlsx
@@ -453,7 +453,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
     <col width="23" customWidth="1" min="14" max="14"/>
     <col width="23" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
@@ -585,16 +585,16 @@
         <v>0.240122561770043</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.01487682818040873</v>
+        <v>-0.01009179729071892</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1243407678034236</v>
+        <v>0.3084847248985025</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5016534039056355</v>
+        <v>0.4433735466569408</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0005509853363037109</v>
+        <v>0.0004775524139404297</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>0.2161069835484207</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01382198166037124</v>
+        <v>-0.0004025537638566906</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0001361150265613864</v>
+        <v>0.04772235471558978</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05745972893141829</v>
+        <v>0.07080924573480711</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003435611724853516</v>
+        <v>0.002915620803833008</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -695,16 +695,16 @@
         <v>0.2324054831704828</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.00895315061721659</v>
+        <v>0.02382735540224331</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05253091296138067</v>
+        <v>0.04615754712081695</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1137540746108816</v>
+        <v>0.1567662682721993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0003705024719238281</v>
+        <v>0.0004670619964599609</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -750,16 +750,16 @@
         <v>0.2521360924102572</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002378964036763844</v>
+        <v>-0.006971901919466531</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01997059654956247</v>
+        <v>0.02693107810969927</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03252571602281806</v>
+        <v>0.01033607103824093</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003354310989379883</v>
+        <v>0.00037384033203125</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -805,16 +805,16 @@
         <v>0.4722306457136356</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02202588933269249</v>
+        <v>-0.02084642631517957</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.06351759186169516</v>
+        <v>-0.09075970693664878</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03034236634852726</v>
+        <v>0.1421751029845515</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005502700805664062</v>
+        <v>0.0007359981536865234</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         <v>0.4729710963640188</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01339415011084228</v>
+        <v>-0.01401413144719679</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00512983418523805</v>
+        <v>-0.00211150254122087</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.03527947037138877</v>
+        <v>0.1411090566692723</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0005972385406494141</v>
+        <v>0.0005788803100585938</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         <v>1.134653468628199</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.002218995264653381</v>
+        <v>0.05599511735653336</v>
       </c>
       <c r="N8" t="n">
-        <v>0.00365734907877582</v>
+        <v>0.07304141166506281</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05320476099839876</v>
+        <v>0.06625666841670115</v>
       </c>
       <c r="P8" t="n">
-        <v>0.008507490158081055</v>
+        <v>0.008950233459472656</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -970,16 +970,16 @@
         <v>1.254338731946513</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02898870311051417</v>
+        <v>0.02354766815091204</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06790207403199719</v>
+        <v>0.01499355233132359</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09405967471274275</v>
+        <v>0.003171235051597186</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007846832275390625</v>
+        <v>0.01735019683837891</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         <v>1.105349407590158</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.003203738030492594</v>
+        <v>0.02520293860190884</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01374401267961648</v>
+        <v>-0.001101898812067016</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1010977649417705</v>
+        <v>0.09796385013728016</v>
       </c>
       <c r="P10" t="n">
-        <v>0.008417844772338867</v>
+        <v>0.0110633373260498</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1080,16 +1080,16 @@
         <v>1.075746177965442</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008425145719275065</v>
+        <v>0.01368122684558237</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1158581273176713</v>
+        <v>0.01258494931909662</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1718444165250167</v>
+        <v>0.07898246948165828</v>
       </c>
       <c r="P11" t="n">
-        <v>0.00820159912109375</v>
+        <v>0.01078343391418457</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0.9139047821010463</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01732693543341739</v>
+        <v>-0.08803010629332136</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1911283651513789</v>
+        <v>-0.002547114096408491</v>
       </c>
       <c r="O12" t="n">
-        <v>0.185369845332556</v>
+        <v>-0.2544630894147459</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0004484653472900391</v>
+        <v>0.0004947185516357422</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         <v>0.9804129908856749</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.05347356404569381</v>
+        <v>0.03079244721570711</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1799033752037129</v>
+        <v>0.0545687482026944</v>
       </c>
       <c r="O13" t="n">
-        <v>0.174618457086223</v>
+        <v>-0.01553090861346694</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0004687309265136719</v>
+        <v>0.0004918575286865234</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
